--- a/output/spreadsheet/startpray-progress-tracker.xlsx
+++ b/output/spreadsheet/startpray-progress-tracker.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>dee4b64</t>
+          <t>fd5493d</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10 19:36:25</t>
+          <t>2026-05-23 12:03:24</t>
         </is>
       </c>
     </row>
@@ -3647,7 +3647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4267,14 +4267,80 @@
           <t>[AUTO] Commit recorded: main @ dee4b64</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
           <t>Continue task updates and prepare push.</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
+        <is>
+          <t>git-hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-05-12 23:39:45</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>[AUTO] Commit recorded: main @ b6d027d</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Continue task updates and prepare push.</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>git-hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-05-23 12:03:01</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>[AUTO] Commit recorded: main @ ae2e854</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Continue task updates and prepare push.</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>git-hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-05-23 12:03:24</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>[AUTO] Commit recorded: main @ fd5493d</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Continue task updates and prepare push.</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
         <is>
           <t>git-hook</t>
         </is>
@@ -4411,7 +4477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5432,7 +5498,118 @@
           <t>https://github.com/dan40912/Start-Pray.git</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-05-12 23:39:45</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>b6d027d</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Improve prayer sharing reports and guest posting</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://github.com/dan40912/Start-Pray.git</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-05-23 12:03:01</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>ae2e854</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Improve public prayer experience</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://github.com/dan40912/Start-Pray.git</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-05-23 12:03:24</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>fd5493d</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Improve public prayer experience</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://github.com/dan40912/Start-Pray.git</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/spreadsheet/startpray-progress-tracker.xlsx
+++ b/output/spreadsheet/startpray-progress-tracker.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>fd5493d</t>
+          <t>2899667</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-05-23 12:03:24</t>
+          <t>2026-05-30 18:44:48</t>
         </is>
       </c>
     </row>
@@ -3647,7 +3647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4333,14 +4333,124 @@
           <t>[AUTO] Commit recorded: main @ fd5493d</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
           <t>Continue task updates and prepare push.</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
+        <is>
+          <t>git-hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-05-30 09:13:43</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>[AUTO] Commit recorded: main @ 9d44c72</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Continue task updates and prepare push.</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>git-hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-05-30 09:39:39</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>[AUTO] Commit recorded: main @ 7aef01f</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Continue task updates and prepare push.</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>git-hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-05-30 09:42:51</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>[AUTO] Commit recorded: main @ a27271e</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Continue task updates and prepare push.</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>git-hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-05-30 18:44:11</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>[AUTO] Commit recorded: main @ aa29e0b</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Continue task updates and prepare push.</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>git-hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-05-30 18:44:48</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>[AUTO] Commit recorded: main @ 2899667</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Continue task updates and prepare push.</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
         <is>
           <t>git-hook</t>
         </is>
@@ -4477,7 +4587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5609,7 +5719,192 @@
           <t>https://github.com/dan40912/Start-Pray.git</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-05-30 09:13:43</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>9d44c72</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Improve localized prayer room experience</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://github.com/dan40912/Start-Pray.git</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-05-30 09:39:39</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>7aef01f</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Stabilize homepage globe and prod deploy</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://github.com/dan40912/Start-Pray.git</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-05-30 09:42:51</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>a27271e</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Start global prayer room from Taiwan</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://github.com/dan40912/Start-Pray.git</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-05-30 18:44:11</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>aa29e0b</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Release Start Pray 2.1.0</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://github.com/dan40912/Start-Pray.git</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-05-30 18:44:48</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2899667</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Release Start Pray 2.1.0</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://github.com/dan40912/Start-Pray.git</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/spreadsheet/startpray-progress-tracker.xlsx
+++ b/output/spreadsheet/startpray-progress-tracker.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2899667</t>
+          <t>457fe5d</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-05-30 18:44:48</t>
+          <t>2026-05-30 18:57:53</t>
         </is>
       </c>
     </row>
@@ -3647,7 +3647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4443,14 +4443,36 @@
           <t>[AUTO] Commit recorded: main @ 2899667</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
           <t>Continue task updates and prepare push.</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
+        <is>
+          <t>git-hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-05-30 18:57:53</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>[AUTO] Commit recorded: main @ 457fe5d</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Continue task updates and prepare push.</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
         <is>
           <t>git-hook</t>
         </is>
@@ -4587,7 +4609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5904,7 +5926,44 @@
           <t>https://github.com/dan40912/Start-Pray.git</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-05-30 18:57:53</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>457fe5d</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Stabilize global prayer room map loading</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://github.com/dan40912/Start-Pray.git</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/spreadsheet/startpray-progress-tracker.xlsx
+++ b/output/spreadsheet/startpray-progress-tracker.xlsx
@@ -582,7 +582,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>feature/roadmap-prd-implementation</t>
         </is>
       </c>
     </row>
@@ -599,7 +599,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>457fe5d</t>
+          <t>753a726</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-05-30 18:57:53</t>
+          <t>2026-07-14 23:16:44</t>
         </is>
       </c>
     </row>
@@ -3647,7 +3647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4465,14 +4465,36 @@
           <t>[AUTO] Commit recorded: main @ 457fe5d</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
           <t>Continue task updates and prepare push.</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
+        <is>
+          <t>git-hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-07-14 23:16:44</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>[AUTO] Commit recorded: feature/roadmap-prd-implementation @ 753a726</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Continue task updates and prepare push.</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
         <is>
           <t>git-hook</t>
         </is>
@@ -4609,7 +4631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5963,7 +5985,44 @@
           <t>https://github.com/dan40912/Start-Pray.git</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-07-14 23:16:44</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>feature/roadmap-prd-implementation</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>753a726</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Implement roadmap PRDs and prayer experience updates</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://github.com/dan40912/Start-Pray.git</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/spreadsheet/startpray-progress-tracker.xlsx
+++ b/output/spreadsheet/startpray-progress-tracker.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>753a726</t>
+          <t>8068c33</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-07-14 23:16:44</t>
+          <t>2026-07-14 23:45:50</t>
         </is>
       </c>
     </row>
@@ -3647,7 +3647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4487,14 +4487,36 @@
           <t>[AUTO] Commit recorded: feature/roadmap-prd-implementation @ 753a726</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
           <t>Continue task updates and prepare push.</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
+        <is>
+          <t>git-hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-07-14 23:45:50</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>[AUTO] Commit recorded: feature/roadmap-prd-implementation @ 8068c33</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Continue task updates and prepare push.</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
         <is>
           <t>git-hook</t>
         </is>
@@ -4631,7 +4653,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6022,7 +6044,44 @@
           <t>https://github.com/dan40912/Start-Pray.git</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-07-14 23:45:50</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>feature/roadmap-prd-implementation</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>8068c33</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Protect anonymous prayer response identities</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://github.com/dan40912/Start-Pray.git</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/spreadsheet/startpray-progress-tracker.xlsx
+++ b/output/spreadsheet/startpray-progress-tracker.xlsx
@@ -582,7 +582,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>feature/roadmap-prd-implementation</t>
+          <t>main</t>
         </is>
       </c>
     </row>
@@ -599,7 +599,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>8068c33</t>
+          <t>89bcc02</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-07-14 23:45:50</t>
+          <t>2026-07-15 00:07:16</t>
         </is>
       </c>
     </row>
@@ -3647,7 +3647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4509,14 +4509,36 @@
           <t>[AUTO] Commit recorded: feature/roadmap-prd-implementation @ 8068c33</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
           <t>Continue task updates and prepare push.</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
+        <is>
+          <t>git-hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-07-15 00:07:16</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>[AUTO] Commit recorded: main @ 89bcc02</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Continue task updates and prepare push.</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
         <is>
           <t>git-hook</t>
         </is>
@@ -4653,7 +4675,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6081,7 +6103,44 @@
           <t>https://github.com/dan40912/Start-Pray.git</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-07-15 00:07:16</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>89bcc02</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Merge feature/roadmap-prd-implementation into main</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://github.com/dan40912/Start-Pray.git</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/spreadsheet/startpray-progress-tracker.xlsx
+++ b/output/spreadsheet/startpray-progress-tracker.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>89bcc02</t>
+          <t>694b927</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-07-15 00:07:16</t>
+          <t>2026-07-15 00:18:28</t>
         </is>
       </c>
     </row>
@@ -3647,7 +3647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4531,14 +4531,36 @@
           <t>[AUTO] Commit recorded: main @ 89bcc02</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
           <t>Continue task updates and prepare push.</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
+        <is>
+          <t>git-hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-07-15 00:18:28</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>[AUTO] Commit recorded: main @ 694b927</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Continue task updates and prepare push.</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
         <is>
           <t>git-hook</t>
         </is>
@@ -4675,7 +4697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6140,7 +6162,44 @@
           <t>https://github.com/dan40912/Start-Pray.git</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-07-15 00:18:28</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>694b927</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Harden production database migration rollout</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://github.com/dan40912/Start-Pray.git</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/spreadsheet/startpray-progress-tracker.xlsx
+++ b/output/spreadsheet/startpray-progress-tracker.xlsx
@@ -582,7 +582,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>fix/admin-visibility-and-voice-experience</t>
         </is>
       </c>
     </row>
@@ -599,7 +599,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>694b927</t>
+          <t>4c52a82</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-07-15 00:18:28</t>
+          <t>2026-09-07 00:50:12</t>
         </is>
       </c>
     </row>
@@ -3647,7 +3647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4553,14 +4553,476 @@
           <t>[AUTO] Commit recorded: main @ 694b927</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
           <t>Continue task updates and prepare push.</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
+        <is>
+          <t>git-hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-08-04 00:25:11</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>[AUTO] Commit recorded: poc/minimal-prayer-redesign @ 6b8cc84</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Continue task updates and prepare push.</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>git-hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-08-04 00:35:37</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>[AUTO] Commit recorded: poc/minimal-prayer-redesign @ 04538e7</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Continue task updates and prepare push.</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>git-hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-08-04 01:49:17</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>[AUTO] Commit recorded: poc/minimal-prayer-redesign @ a69ae05</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Continue task updates and prepare push.</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>git-hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-08-04 01:56:23</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>[AUTO] Commit recorded: poc/minimal-prayer-redesign @ 4eaea7e</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Continue task updates and prepare push.</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>git-hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-08-04 02:02:04</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>[AUTO] Commit recorded: poc/minimal-prayer-redesign @ 78103e0</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Continue task updates and prepare push.</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>git-hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-08-04 08:32:58</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>[AUTO] Commit recorded: poc/minimal-prayer-redesign @ 51b2ee4</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Continue task updates and prepare push.</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>git-hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-08-04 23:01:03</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>[AUTO] Commit recorded: poc/minimal-prayer-redesign @ ed43015</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Continue task updates and prepare push.</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>git-hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-08-04 23:49:04</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>[AUTO] Commit recorded: poc/minimal-prayer-redesign @ d485b04</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Continue task updates and prepare push.</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>git-hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-08-05 00:57:50</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>[AUTO] Commit recorded: poc/minimal-prayer-redesign @ 4f13d72</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Continue task updates and prepare push.</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>git-hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-08-05 21:35:54</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>[AUTO] Commit recorded: poc/minimal-prayer-redesign @ 70a6bb5</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Continue task updates and prepare push.</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>git-hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:00:18</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>[AUTO] Commit recorded: poc/minimal-prayer-redesign @ d0561ce</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Continue task updates and prepare push.</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>git-hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:02</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>[AUTO] Commit recorded: poc/minimal-prayer-redesign @ c6b5b7d</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Continue task updates and prepare push.</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>git-hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-09-05 17:23:36</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>[AUTO] Commit recorded: poc/minimal-prayer-redesign @ 65961ab</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Continue task updates and prepare push.</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>git-hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-09-05 17:23:54</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>[AUTO] Commit recorded: poc/minimal-prayer-redesign @ 1f3c64f</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Continue task updates and prepare push.</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>git-hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-09-05 17:24:14</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>[AUTO] Commit recorded: poc/minimal-prayer-redesign @ 2010830</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Continue task updates and prepare push.</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>git-hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-09-05 17:24:38</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>[AUTO] Commit recorded: poc/minimal-prayer-redesign @ d745f05</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Continue task updates and prepare push.</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>git-hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-05 17:29:15</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>[AUTO] Commit recorded: poc/minimal-prayer-redesign @ ab41479</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Continue task updates and prepare push.</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>git-hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-09-07 00:49:09</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>[AUTO] Commit recorded: fix/admin-visibility-and-voice-experience @ b63b440</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Continue task updates and prepare push.</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>git-hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-09-07 00:49:36</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>[AUTO] Commit recorded: fix/admin-visibility-and-voice-experience @ aa45cf8</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Continue task updates and prepare push.</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>git-hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-09-07 00:50:01</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>[AUTO] Commit recorded: fix/admin-visibility-and-voice-experience @ a289c51</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Continue task updates and prepare push.</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>git-hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-07 00:50:12</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>[AUTO] Commit recorded: fix/admin-visibility-and-voice-experience @ 4c52a82</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Continue task updates and prepare push.</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
         <is>
           <t>git-hook</t>
         </is>
@@ -4697,7 +5159,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6199,7 +6661,784 @@
           <t>https://github.com/dan40912/Start-Pray.git</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-08-04 00:25:11</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>poc/minimal-prayer-redesign</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>6b8cc84</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>refactor: simplify account and global navigation</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://github.com/dan40912/Start-Pray.git</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-08-04 00:35:37</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>poc/minimal-prayer-redesign</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>04538e7</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>refactor: replace globe hero with minimal prayer entry</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://github.com/dan40912/Start-Pray.git</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-08-04 01:49:17</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>poc/minimal-prayer-redesign</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>a69ae05</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>feat: integrate prayer recording flow into homepage</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://github.com/dan40912/Start-Pray.git</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-08-04 01:56:23</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>poc/minimal-prayer-redesign</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>4eaea7e</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>docs: document current architecture and redesign progress</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://github.com/dan40912/Start-Pray.git</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-08-04 02:02:04</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>poc/minimal-prayer-redesign</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>78103e0</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>docs: design anonymous prayer submission architecture</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://github.com/dan40912/Start-Pray.git</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-08-04 08:32:58</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>poc/minimal-prayer-redesign</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>51b2ee4</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>feat: support anonymous prayer submission</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://github.com/dan40912/Start-Pray.git</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-08-04 23:01:03</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>poc/minimal-prayer-redesign</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>ed43015</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>refactor: present prayer needs as the homepage focus</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://github.com/dan40912/Start-Pray.git</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-08-04 23:49:04</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>poc/minimal-prayer-redesign</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>d485b04</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>feat: add prayer browsing and companion playback</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://github.com/dan40912/Start-Pray.git</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-08-05 00:57:50</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>poc/minimal-prayer-redesign</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>4f13d72</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>refactor: unify anonymous prayer interactions across prayer pages</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://github.com/dan40912/Start-Pray.git</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-08-05 21:35:54</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>poc/minimal-prayer-redesign</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>70a6bb5</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>feat: add anonymous prayed reactions</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://github.com/dan40912/Start-Pray.git</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:00:18</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>poc/minimal-prayer-redesign</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>d0561ce</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>fix: harden prayer interaction flows</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://github.com/dan40912/Start-Pray.git</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:02</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>poc/minimal-prayer-redesign</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>c6b5b7d</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>docs: complete final acceptance and release readiness review</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://github.com/dan40912/Start-Pray.git</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-09-05 17:23:36</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>poc/minimal-prayer-redesign</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>65961ab</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>@ refactor: use site logo for anonymous responder avatars</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://github.com/dan40912/Start-Pray.git</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-09-05 17:23:54</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>poc/minimal-prayer-redesign</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>1f3c64f</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>refactor: use site logo for anonymous responder avatars</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://github.com/dan40912/Start-Pray.git</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-09-05 17:24:14</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>poc/minimal-prayer-redesign</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2010830</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>feat: let card owners attach a 3-minute voice message</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://github.com/dan40912/Start-Pray.git</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-09-05 17:24:38</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>poc/minimal-prayer-redesign</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>d745f05</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>feat: rework the homepage hero and slim down font loading</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://github.com/dan40912/Start-Pray.git</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-09-05 17:29:15</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>poc/minimal-prayer-redesign</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>ab41479</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>docs: add PROD release plan for d745f05</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://github.com/dan40912/Start-Pray.git</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-07 00:49:09</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>fix/admin-visibility-and-voice-experience</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>b63b440</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>fix(admin): repair search and show who is behind anonymous posts</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://github.com/dan40912/Start-Pray.git</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-09-07 00:49:36</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>fix/admin-visibility-and-voice-experience</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>aa45cf8</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>feat(web): bring back account entry points and rework the hero card</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://github.com/dan40912/Start-Pray.git</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-09-07 00:50:01</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>fix/admin-visibility-and-voice-experience</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>a289c51</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>feat(voice): offer text as well as voice, and make recordings audible</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://github.com/dan40912/Start-Pray.git</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-09-07 00:50:12</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>fix/admin-visibility-and-voice-experience</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>4c52a82</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>docs: add a prompt for drafting text replies to unanswered cards</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://github.com/dan40912/Start-Pray.git</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/spreadsheet/startpray-progress-tracker.xlsx
+++ b/output/spreadsheet/startpray-progress-tracker.xlsx
@@ -582,7 +582,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>fix/admin-visibility-and-voice-experience</t>
+          <t>design/phase0-foundation</t>
         </is>
       </c>
     </row>
@@ -599,7 +599,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>4c52a82</t>
+          <t>5b23f1f</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07 00:50:12</t>
+          <t>2026-09-10 00:53:44</t>
         </is>
       </c>
     </row>
@@ -3647,7 +3647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5015,14 +5015,36 @@
           <t>[AUTO] Commit recorded: fix/admin-visibility-and-voice-experience @ 4c52a82</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
           <t>Continue task updates and prepare push.</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
+        <is>
+          <t>git-hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-10 00:53:44</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>[AUTO] Commit recorded: design/phase0-foundation @ 5b23f1f</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Continue task updates and prepare push.</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
         <is>
           <t>git-hook</t>
         </is>
@@ -5159,7 +5181,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:H62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7438,7 +7460,44 @@
           <t>https://github.com/dan40912/Start-Pray.git</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-10 00:53:44</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>design/phase0-foundation</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>5b23f1f</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>refactor(design): collapse eight palettes into one token layer</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://github.com/dan40912/Start-Pray.git</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/spreadsheet/startpray-progress-tracker.xlsx
+++ b/output/spreadsheet/startpray-progress-tracker.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>5b23f1f</t>
+          <t>32a60d6</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10 00:53:44</t>
+          <t>2026-09-10 01:03:36</t>
         </is>
       </c>
     </row>
@@ -3647,7 +3647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:F64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5037,14 +5037,36 @@
           <t>[AUTO] Commit recorded: design/phase0-foundation @ 5b23f1f</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr"/>
-      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
           <t>Continue task updates and prepare push.</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
+        <is>
+          <t>git-hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-09-10 01:03:36</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>[AUTO] Commit recorded: design/phase0-foundation @ 32a60d6</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Continue task updates and prepare push.</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
         <is>
           <t>git-hook</t>
         </is>
@@ -5181,7 +5203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H62"/>
+  <dimension ref="A1:H63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7497,7 +7519,44 @@
           <t>https://github.com/dan40912/Start-Pray.git</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-10 01:03:36</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>design/phase0-foundation</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>32a60d6</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>fix(design): one accent, one vocabulary, one header height</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://github.com/dan40912/Start-Pray.git</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/spreadsheet/startpray-progress-tracker.xlsx
+++ b/output/spreadsheet/startpray-progress-tracker.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>32a60d6</t>
+          <t>6364fd9</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10 01:03:36</t>
+          <t>2026-09-10 01:08:25</t>
         </is>
       </c>
     </row>
@@ -3647,7 +3647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5059,14 +5059,36 @@
           <t>[AUTO] Commit recorded: design/phase0-foundation @ 32a60d6</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr"/>
-      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
           <t>Continue task updates and prepare push.</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
+        <is>
+          <t>git-hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-09-10 01:08:25</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>[AUTO] Commit recorded: design/phase0-foundation @ 6364fd9</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Continue task updates and prepare push.</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
         <is>
           <t>git-hook</t>
         </is>
@@ -5203,7 +5225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H63"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7556,7 +7578,44 @@
           <t>https://github.com/dan40912/Start-Pray.git</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-09-10 01:08:25</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>design/phase0-foundation</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>6364fd9</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>refactor(design): share one card component, keep one CTA per screen</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://github.com/dan40912/Start-Pray.git</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/spreadsheet/startpray-progress-tracker.xlsx
+++ b/output/spreadsheet/startpray-progress-tracker.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>6364fd9</t>
+          <t>56caee1</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10 01:08:25</t>
+          <t>2026-09-10 01:09:28</t>
         </is>
       </c>
     </row>
@@ -3647,7 +3647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5081,14 +5081,36 @@
           <t>[AUTO] Commit recorded: design/phase0-foundation @ 6364fd9</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
           <t>Continue task updates and prepare push.</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
+        <is>
+          <t>git-hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-09-10 01:09:28</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>[AUTO] Commit recorded: design/phase0-foundation @ 56caee1</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Continue task updates and prepare push.</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
         <is>
           <t>git-hook</t>
         </is>
@@ -5225,7 +5247,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H64"/>
+  <dimension ref="A1:H65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7615,7 +7637,44 @@
           <t>https://github.com/dan40912/Start-Pray.git</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-09-10 01:09:28</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>design/phase0-foundation</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>56caee1</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>docs: record what phase 0 landed and hand the rest to the three tracks</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://github.com/dan40912/Start-Pray.git</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/spreadsheet/startpray-progress-tracker.xlsx
+++ b/output/spreadsheet/startpray-progress-tracker.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>56caee1</t>
+          <t>4614b31</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10 01:09:28</t>
+          <t>2026-09-10 01:18:02</t>
         </is>
       </c>
     </row>
@@ -3647,7 +3647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5103,14 +5103,36 @@
           <t>[AUTO] Commit recorded: design/phase0-foundation @ 56caee1</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr"/>
-      <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
           <t>Continue task updates and prepare push.</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
+        <is>
+          <t>git-hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-09-10 01:18:02</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>[AUTO] Commit recorded: design/phase0-foundation @ 4614b31</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Continue task updates and prepare push.</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
         <is>
           <t>git-hook</t>
         </is>
@@ -5247,7 +5269,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H65"/>
+  <dimension ref="A1:H66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7674,7 +7696,44 @@
           <t>https://github.com/dan40912/Start-Pray.git</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-09-10 01:18:02</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>design/phase0-foundation</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>4614b31</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>fix(player): only show the player once someone presses play, and let them close it</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://github.com/dan40912/Start-Pray.git</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/spreadsheet/startpray-progress-tracker.xlsx
+++ b/output/spreadsheet/startpray-progress-tracker.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>4614b31</t>
+          <t>74767fa</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10 01:18:02</t>
+          <t>2026-09-10 01:21:46</t>
         </is>
       </c>
     </row>
@@ -3647,7 +3647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F67"/>
+  <dimension ref="A1:F68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5125,14 +5125,36 @@
           <t>[AUTO] Commit recorded: design/phase0-foundation @ 4614b31</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr"/>
-      <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
           <t>Continue task updates and prepare push.</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
+        <is>
+          <t>git-hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-09-10 01:21:46</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>[AUTO] Commit recorded: design/phase0-foundation @ 74767fa</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Continue task updates and prepare push.</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
         <is>
           <t>git-hook</t>
         </is>
@@ -5269,7 +5291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H66"/>
+  <dimension ref="A1:H67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7733,7 +7755,44 @@
           <t>https://github.com/dan40912/Start-Pray.git</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-09-10 01:21:46</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>design/phase0-foundation</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>74767fa</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>fix(home,responses): stop the page contradicting itself, and let the replies read as people</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://github.com/dan40912/Start-Pray.git</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/spreadsheet/startpray-progress-tracker.xlsx
+++ b/output/spreadsheet/startpray-progress-tracker.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>74767fa</t>
+          <t>b01c975</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10 01:21:46</t>
+          <t>2026-09-10 01:31:21</t>
         </is>
       </c>
     </row>
@@ -3647,7 +3647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F68"/>
+  <dimension ref="A1:F69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5147,14 +5147,36 @@
           <t>[AUTO] Commit recorded: design/phase0-foundation @ 74767fa</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr"/>
-      <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
           <t>Continue task updates and prepare push.</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
+        <is>
+          <t>git-hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-09-10 01:31:21</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>[AUTO] Commit recorded: design/phase0-foundation @ b01c975</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Continue task updates and prepare push.</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
         <is>
           <t>git-hook</t>
         </is>
@@ -5291,7 +5313,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H67"/>
+  <dimension ref="A1:H68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7792,7 +7814,44 @@
           <t>https://github.com/dan40912/Start-Pray.git</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-09-10 01:31:21</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>design/phase0-foundation</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>b01c975</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>feat(account): move the account flow onto the day surface, and lead with prayer</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://github.com/dan40912/Start-Pray.git</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/spreadsheet/startpray-progress-tracker.xlsx
+++ b/output/spreadsheet/startpray-progress-tracker.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>b01c975</t>
+          <t>a22d0ff</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10 01:31:21</t>
+          <t>2026-09-10 01:39:55</t>
         </is>
       </c>
     </row>
@@ -3647,7 +3647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F69"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5169,14 +5169,36 @@
           <t>[AUTO] Commit recorded: design/phase0-foundation @ b01c975</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr"/>
-      <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
           <t>Continue task updates and prepare push.</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
+        <is>
+          <t>git-hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-09-10 01:39:55</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>[AUTO] Commit recorded: design/phase0-foundation @ a22d0ff</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Continue task updates and prepare push.</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
         <is>
           <t>git-hook</t>
         </is>
@@ -5313,7 +5335,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7851,7 +7873,44 @@
           <t>https://github.com/dan40912/Start-Pray.git</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-09-10 01:39:55</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>design/phase0-foundation</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>a22d0ff</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>feat(home): make the hero a deck you can actually flick through</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://github.com/dan40912/Start-Pray.git</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/spreadsheet/startpray-progress-tracker.xlsx
+++ b/output/spreadsheet/startpray-progress-tracker.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>a22d0ff</t>
+          <t>372571e</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10 01:39:55</t>
+          <t>2026-09-10 01:41:49</t>
         </is>
       </c>
     </row>
@@ -3647,7 +3647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5191,14 +5191,36 @@
           <t>[AUTO] Commit recorded: design/phase0-foundation @ a22d0ff</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr"/>
-      <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
           <t>Continue task updates and prepare push.</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
+        <is>
+          <t>git-hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-09-10 01:41:49</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>[AUTO] Commit recorded: design/phase0-foundation @ 372571e</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Continue task updates and prepare push.</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
         <is>
           <t>git-hook</t>
         </is>
@@ -5335,7 +5357,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H69"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7910,7 +7932,44 @@
           <t>https://github.com/dan40912/Start-Pray.git</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-09-10 01:41:49</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>design/phase0-foundation</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>372571e</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>refactor(routes): the member area is /me, not /customer-portal</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://github.com/dan40912/Start-Pray.git</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/spreadsheet/startpray-progress-tracker.xlsx
+++ b/output/spreadsheet/startpray-progress-tracker.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>372571e</t>
+          <t>869055a</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10 01:41:49</t>
+          <t>2026-09-10 01:45:30</t>
         </is>
       </c>
     </row>
@@ -3647,7 +3647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F71"/>
+  <dimension ref="A1:F72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5213,14 +5213,36 @@
           <t>[AUTO] Commit recorded: design/phase0-foundation @ 372571e</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr"/>
-      <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
           <t>Continue task updates and prepare push.</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
+        <is>
+          <t>git-hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-09-10 01:45:30</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>[AUTO] Commit recorded: design/phase0-foundation @ 869055a</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Continue task updates and prepare push.</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
         <is>
           <t>git-hook</t>
         </is>
@@ -5357,7 +5379,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H70"/>
+  <dimension ref="A1:H71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7969,7 +7991,44 @@
           <t>https://github.com/dan40912/Start-Pray.git</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-09-10 01:45:30</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>design/phase0-foundation</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>869055a</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>fix(prayer-room): stop the map controls stretching across the globe</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://github.com/dan40912/Start-Pray.git</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/spreadsheet/startpray-progress-tracker.xlsx
+++ b/output/spreadsheet/startpray-progress-tracker.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>869055a</t>
+          <t>e8f9c3b</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10 01:45:30</t>
+          <t>2026-09-11 21:40:00</t>
         </is>
       </c>
     </row>
@@ -3647,7 +3647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F72"/>
+  <dimension ref="A1:F78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5235,14 +5235,146 @@
           <t>[AUTO] Commit recorded: design/phase0-foundation @ 869055a</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr"/>
-      <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
           <t>Continue task updates and prepare push.</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
+        <is>
+          <t>git-hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-09-10 08:40:15</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>[AUTO] Commit recorded: design/phase0-foundation @ 98c0023</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Continue task updates and prepare push.</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>git-hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-09-11 20:58:33</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>[AUTO] Commit recorded: design/phase0-foundation @ 1826857</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Continue task updates and prepare push.</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>git-hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-09-11 21:39:06</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>[AUTO] Commit recorded: design/phase0-foundation @ 4ba2705</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Continue task updates and prepare push.</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>git-hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-09-11 21:39:07</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>[AUTO] Commit recorded: design/phase0-foundation @ 232f031</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Continue task updates and prepare push.</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>git-hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-09-11 21:39:59</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>[AUTO] Commit recorded: design/phase0-foundation @ 338dea8</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Continue task updates and prepare push.</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>git-hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-09-11 21:40:00</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>[AUTO] Commit recorded: design/phase0-foundation @ e8f9c3b</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Continue task updates and prepare push.</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
         <is>
           <t>git-hook</t>
         </is>
@@ -5379,7 +5511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H71"/>
+  <dimension ref="A1:H77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -8028,7 +8160,229 @@
           <t>https://github.com/dan40912/Start-Pray.git</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-09-10 08:40:15</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>design/phase0-foundation</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>98c0023</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>fix(design): repairs found by testing the branch</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://github.com/dan40912/Start-Pray.git</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-09-11 20:58:33</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>design/phase0-foundation</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>1826857</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>feat(recorder): move on to the next prayer three seconds after sending</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://github.com/dan40912/Start-Pray.git</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-09-11 21:39:06</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>design/phase0-foundation</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>4ba2705</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>feat(terms,home): rewrite /terms around the upload rules, and bring the stats back</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://github.com/dan40912/Start-Pray.git</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-09-11 21:39:07</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>design/phase0-foundation</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>232f031</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>fix(surface): keep &lt;html data-surface&gt; in sync on client-side navigation</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://github.com/dan40912/Start-Pray.git</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-09-11 21:39:59</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>design/phase0-foundation</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>338dea8</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>refactor(player): fold the companion overlay into the one global player</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://github.com/dan40912/Start-Pray.git</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-09-11 21:40:00</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>design/phase0-foundation</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>e8f9c3b</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>feat(nav): show the global prayer room entry again</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://github.com/dan40912/Start-Pray.git</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/spreadsheet/startpray-progress-tracker.xlsx
+++ b/output/spreadsheet/startpray-progress-tracker.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>e8f9c3b</t>
+          <t>1ab8502</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11 21:40:00</t>
+          <t>2026-09-12 14:44:50</t>
         </is>
       </c>
     </row>
@@ -3647,7 +3647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F78"/>
+  <dimension ref="A1:F80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5367,14 +5367,58 @@
           <t>[AUTO] Commit recorded: design/phase0-foundation @ e8f9c3b</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr"/>
-      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
           <t>Continue task updates and prepare push.</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
+        <is>
+          <t>git-hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-09-11 21:40:01</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>[AUTO] Commit recorded: design/phase0-foundation @ 4216c36</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Continue task updates and prepare push.</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>git-hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-09-12 14:44:50</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>[AUTO] Commit recorded: design/phase0-foundation @ 1ab8502</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Continue task updates and prepare push.</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
         <is>
           <t>git-hook</t>
         </is>
@@ -5511,7 +5555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H77"/>
+  <dimension ref="A1:H79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -8382,7 +8426,81 @@
           <t>https://github.com/dan40912/Start-Pray.git</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-09-11 21:40:01</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>design/phase0-foundation</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>4216c36</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>chore: update progress tracker</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://github.com/dan40912/Start-Pray.git</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-09-12 14:44:50</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>design/phase0-foundation</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>1ab8502</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>feat(home,prayfor): pick a spot on the globe, loop the hero, sort the wall</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://github.com/dan40912/Start-Pray.git</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
